--- a/analiza/Pavva_produse_lipsa_site.xlsx
+++ b/analiza/Pavva_produse_lipsa_site.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
@@ -70,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B0F28"/>
+        <fgColor rgb="00FBE3D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE3D6"/>
+        <fgColor rgb="00FFF4CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,7 +90,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4CC"/>
+        <fgColor rgb="001B0F28"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,19 +128,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -503,11 +521,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -605,15 +623,192 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Tab-uri: Produse site · Symmetrica vs site · Lipsesc de pe site · Lipsesc din catalog Pavva</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Cum se citește coloana „Sursă” (tab-ul „Lipsesc de pe site”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Symmetrica + Pavva</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e și în catalogul Symmetrica, și în lista de prețuri Pavva. Sigur îl avem → se încarcă PRIMUL pe site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Doar Symmetrica</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e în catalogul Symmetrica, dar NU apare în lista de prețuri Pavva. Trebuie confirmat dacă îl producem → se încarcă doar după confirmare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Doar Pavva</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e doar în lista de prețuri Pavva (nu și în Symmetrica, care e catalog doar pentru casă și grădină, fără produse industriale). Îl vindem → se încarcă după cele roșii.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Culori în tab-ul „Symmetrica vs site”</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Lipsește de pe site</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e în catalogul Symmetrica, dar nu e pe site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e deja pe site (coloana „Nume pe site” arată cum se numește acolo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ce conține fiecare tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Rezumat</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Cifrele principale (se calculează automat din celelalte tab-uri) și această legendă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Produse site</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Toate produsele publicate acum pe site, pe categorii, cu link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Symmetrica vs site</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Fiecare produs din catalogul Symmetrica: e sau nu pe site, și codul lui din lista de prețuri Pavva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Lipsesc de pe site</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Lista completă de produse de încărcat pe site: categoria propusă, coduri, grosime, dimensiuni, culori, pagina din catalog. Filtrează după „Sursă” (săgeata din capul coloanei).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Lipsesc din catalog Pavva</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Produsele din Symmetrica care nu apar deloc în lista de prețuri Pavva (aceleași ca „Doar Symmetrica”).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Coloane</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Categorie pe site (propusă)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de pe site în care ar intra produsul (gama Symmetrica Select = „Pavele Premium” pe site).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Cod Pavva</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Codul PAV din lista de prețuri Pavva 2026 (gol = nu apare acolo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Pag. catalog Pavva / Symmetrica</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Pagina din PDF unde se găsește produsul, pentru poze și detalii.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Surse: staging.pavva.ro (produsele publicate), „Listă de prețuri 2026” Pavva, „Catalog Symmetrica ediția 2023”.</t>
         </is>
@@ -639,17 +834,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Produs</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -1500,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1511,2337 +1706,2364 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Gamă Symmetrica</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Produs Symmetrica</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Pagina catalog Symmetrica</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Pe site?</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Nume pe site</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>În catalog Pavva?</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Cod Pavva</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Legendă</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Linea Emotione Mix Color</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr"/>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Emotione – PAV 231</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Lipsește de pe site</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>În catalogul Symmetrica, dar nu e pe site.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Linea Emotione Abrasio</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr"/>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr"/>
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Deja pe site.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Magna</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>PAV 234</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Kombi</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Kombi</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>PAV 311 / 310 / 331</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bareto</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr"/>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Alegria Antica</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Alegria Antica</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>PAV 04</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Plaza Antica</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Plaza Antica</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>PAV 113</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Arco Antica</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Arco Antica</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Arco</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Arco</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Arco Granito</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Arca Romana</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Arca Romana Granito</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr"/>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Retta Granito</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>PAV 15</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Cammino Granito</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>PAV 21</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Quadra Granito</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>PAV 14</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Amplio Granito</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>PAV 48</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Retta Onda</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr"/>
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Cammino Onda</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Quadra Onda</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr"/>
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Travia Mix Color</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Cammino Mix Color</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Cammino Mix Color</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>PAV 235</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Amplio Mix Color</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Amplio Mix Color</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>PAV 09 / 228</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Maxia Mix Color</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Lastra Natura</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr"/>
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Immagia</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Immagia</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>PAV 94 / 95</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Kit pentru grădină Yucatan</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Kit pentru grădină Yucatan</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>PAV 85 / 86 / 108 / 175 / 176</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Kit pentru grădină Yucatan Antica</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Kit pentru gradina Yucatan Antica</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>PAV 85 / 86 / 108 / 175 / 176</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>Dală mare acoperire</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Dală mare acoperire</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>PAV 51</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Kit pentru grădină Gardeo</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Kit pentru garduri Gardeo</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>PAV 81 / 82 / 293 / 294</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Element placare Rock</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Elemente placare Rock</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>PAV 99</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Element placare Rock Antica</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Elemente placare Rock Antica</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>PAV 99</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Treaptă grădină</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Treaptă grădină</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>PAV 78 / 79</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Safirio</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>PAV 330</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Sarmia</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr"/>
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Alegria</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Alegria</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>PAV 44 / 04 / 03</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Practico</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Cammino</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Cammino</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>PAV 21 / 25</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Quadra</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Quadra</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>PAV 14 / 88</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Retta</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Retta</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>PAV 24 / 15 / 19 / 60</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Kubik</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Kubik</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>PAV 12</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Dublu „T”</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Dublu „T”</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>PAV 02 / 01 / 26</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>Mirage</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Mirage</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>PAV 23</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>Dale</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>Amplio</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Amplio</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>PAV 407 / 09 / 48</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Dale</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>Tetra</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Tetra</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>PAV 110 / 227</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Dale</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>Eco Natura</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Eco Natura</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
         <is>
           <t>PAV 72 / 22</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Bordură Rock (SYMM 116)</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>35, 53</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr"/>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr"/>
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 30</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 30</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>PAV 30</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 303</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 303</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>PAV 303</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Bordură Practico (SYMM 91)</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr"/>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr"/>
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>Nu</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 37</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>52, 55</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 37</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>PAV 37</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 64</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>52, 55</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 64</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>PAV 64</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 57</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 57</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>PAV 57</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>Bordură mijlocie SYMM 73</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>Bordura mijlocie PAVV 73</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>PAV 73</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="H54" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>Bordură mijlocie SYMM 31</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>Bordura mijlocie PAVV 31</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
         <is>
           <t>PAV 31</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="H55" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>Bordură mijlocie SYMM 92</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>Bordura mijlocie PAVV 92</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>PAV 92</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Rigole</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>Rigolă mică (SYMM 39)</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>Rigolă mare și mică</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
         <is>
           <t>PAV 39</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Rigole</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="13" t="inlineStr">
         <is>
           <t>Rigolă mare (SYMM 35)</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>Rigolă mare și mică</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>PAV 35</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="H58" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Rigole</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>Rigolă pietonală (SYMM 125)</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>Rigolă pietonală</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>PAV 323</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="H59" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
@@ -3859,7 +4081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3872,1043 +4094,1080 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Nr.</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Produs</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Categorie pe site (propusă)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Sursă</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Cod Pavva</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Pag. catalog Pavva</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Pag. catalog Symmetrica</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Grosime</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Dimensiuni</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Culori</t>
         </is>
       </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Legendă</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Arco Granito</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>115×85, 115×73×102, 115×115 mm (3 forme)</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem</t>
         </is>
       </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Symmetrica + Pavva</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e și în catalogul Symmetrica, și în lista de prețuri Pavva. Sigur îl avem → se încarcă PRIMUL pe site.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Retta Granito</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>PAV 15</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>200×100 mm</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Doar Symmetrica</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e în catalogul Symmetrica, dar NU apare în lista de prețuri Pavva. Trebuie confirmat dacă îl producem → se încarcă doar după confirmare.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Quadra Granito</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>PAV 14</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>200×200 mm</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Doar Pavva</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e doar în lista de prețuri Pavva (nu și în Symmetrica, care e catalog doar pentru casă și grădină, fără produse industriale). Îl vindem → se încarcă după cele roșii.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Cammino Granito</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>PAV 21</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>300×200 mm</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Amplio Granito</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>PAV 48</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>400×400 mm</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Magna</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>PAV 234</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>400×300 mm</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>crem-maro, alb-portocaliu-antracit, alb-travertin, alb-antracit</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Linea Emotione Mix Color (Emotione)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>PAV 231</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>Pavva: 600×300 mm · Symmetrica: 20×30, 30×30, 30×40, 30×60, 20×40, 40×40, 40×60 cm</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>crem-maro, alb-portocaliu-antracit, alb-antracit, alb-travertin</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Safirio</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Pavele Standard</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>PAV 330</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Pavva 6 cm · Symmetrica 4 cm</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>140×140 mm</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>alb, gri, antracit</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Linea Emotione Abrasio</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>20×30, 30×30, 30×40, 30×60, 20×40, 40×40, 40×60 cm</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>alb, gri, antracit, crem, maro</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Bareto</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>8 cm</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>30/40/50 × 12,5 și 30/40/50 × 16,5 cm (pachet)</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>alb, gri, antracit</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Arca Romana</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr"/>
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>12×16,5, 12×13, 12×10,5, 12×12, 12×18 cm (pachet 1 mp)</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>alb, gri, antracit, roșu, maro, portocaliu, crem</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Arca Romana Granito</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>12×16,5, 12×13, 12×10,5, 12×12, 12×18 cm (pachet 1 mp)</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>alb, gri, antracit, portocaliu, roșu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Retta Onda</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="9" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr"/>
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>20×10 cm</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Cammino Onda</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>20×30 cm</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Quadra Onda</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr"/>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>20×20 cm</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>Travia Mix Color</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr"/>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>21×14, 14×14 cm (pachet 1,1 mp)</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Maxia Mix Color</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>10 cm</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>80×62 cm</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>alb, gri, antracit, alb-antracit, alb-portocaliu, portocaliu-antracit</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Lastra Natura</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>54×36, 36×36, 18×36 cm</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>portocaliu-antracit, gri-portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Sarmia</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Pavele Standard</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr"/>
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>25×15 cm</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>alb, gri, antracit</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Practico</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>Pavele Standard</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>4 cm și 7 cm</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>15×10 cm</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>gri, antracit, roșu, maro, portocaliu</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Bordură Rock (SYMM 116)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>35, 53</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>înălțime 12 cm</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>50×10 cm</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>gri, gri-portocaliu-antracit</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Bordură Practico (SYMM 91)</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>12 cm</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>24×6 cm</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>gri, roșu, portocaliu, maro, antracit</t>
         </is>
@@ -5906,42 +6165,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Nr.</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Produs Symmetrica</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Categorie pe site (propusă)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Pagina catalog Symmetrica</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Grosime</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Dimensiuni</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Culori</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Pe site?</t>
         </is>

--- a/analiza/Pavva_produse_lipsa_site.xlsx
+++ b/analiza/Pavva_produse_lipsa_site.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Rezumat" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Produse site" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Symmetrica vs site" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lipsesc de pe site" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lipsesc din catalog Pavva" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Toate produsele (culori)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Produse site" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Symmetrica vs site" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lipsesc de pe site" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lipsesc din catalog Pavva" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Produse site'!$A$1:$C$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Symmetrica vs site'!$A$1:$H$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Lipsesc de pe site'!$A$1:$J$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lipsesc din catalog Pavva'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Toate produsele (culori)'!$A$1:$H$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Produse site'!$A$1:$C$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Symmetrica vs site'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lipsesc de pe site'!$A$1:$J$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Lipsesc din catalog Pavva'!$A$1:$H$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,13 +67,39 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -120,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,23 +165,47 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -623,192 +675,270 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Total produse (site + Symmetrica + Pavva), fără dubluri</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>COUNTA('Toate produsele (culori)'!C2:C300)</f>
+        <v/>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Cum se citește coloana „Sursă” (tab-ul „Lipsesc de pe site”)</t>
+          <t>Culori în tab-ul „Toate produsele (culori)”</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Symmetrica + Pavva</t>
+          <t>Verde – Pe site</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Produsul e și în catalogul Symmetrica, și în lista de prețuri Pavva. Sigur îl avem → se încarcă PRIMUL pe site.</t>
+          <t>Produsul e publicat pe site.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Doar Symmetrica</t>
+          <t>Albastru – Symmetrica</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Produsul e în catalogul Symmetrica, dar NU apare în lista de prețuri Pavva. Trebuie confirmat dacă îl producem → se încarcă doar după confirmare.</t>
+          <t>Produsul apare în catalogul Symmetrica 2023.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>Mov – Pavva</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Produsul apare în lista de prețuri Pavva 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Roșu – LIPSEȘTE</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Produsul NU e pe site și trebuie încărcat. Roșul apare doar la produsele care lipsesc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Cum se citește coloana „Sursă” (tab-ul „Lipsesc de pe site”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Symmetrica + Pavva</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e și în catalogul Symmetrica, și în lista de prețuri Pavva. Sigur îl avem → se încarcă PRIMUL pe site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Doar Symmetrica</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e în catalogul Symmetrica, dar NU apare în lista de prețuri Pavva. Trebuie confirmat dacă îl producem → se încarcă doar după confirmare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
           <t>Doar Pavva</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Produsul e doar în lista de prețuri Pavva (nu și în Symmetrica, care e catalog doar pentru casă și grădină, fără produse industriale). Îl vindem → se încarcă după cele roșii.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Culori în tab-ul „Symmetrica vs site”</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Produsul e în catalogul Symmetrica, dar nu e pe site.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Produsul e deja pe site (coloana „Nume pe site” arată cum se numește acolo).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Ce conține fiecare tab</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Rezumat</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Cifrele principale (se calculează automat din celelalte tab-uri) și această legendă.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Toate produsele (culori)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Toate produsele (site + Symmetrica + Pavva) într-o singură listă, pe categorii: verde = pe site, albastru = în Symmetrica, mov = în Pavva, roșu = lipsește de pe site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Produse site</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Toate produsele publicate acum pe site, pe categorii, cu link.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Symmetrica vs site</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Fiecare produs din catalogul Symmetrica: e sau nu pe site, și codul lui din lista de prețuri Pavva.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Lipsesc de pe site</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Lista completă de produse de încărcat pe site: categoria propusă, coduri, grosime, dimensiuni, culori, pagina din catalog. Filtrează după „Sursă” (săgeata din capul coloanei).</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Lipsesc din catalog Pavva</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Produsele din Symmetrica care nu apar deloc în lista de prețuri Pavva (aceleași ca „Doar Symmetrica”).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Coloane</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Categorie pe site (propusă)</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Categoria de pe site în care ar intra produsul (gama Symmetrica Select = „Pavele Premium” pe site).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Cod Pavva</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Codul PAV din lista de prețuri Pavva 2026 (gol = nu apare acolo).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Pag. catalog Pavva / Symmetrica</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Pagina din PDF unde se găsește produsul, pentru poze și detalii.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Surse: staging.pavva.ro (produsele publicate), „Listă de prețuri 2026” Pavva, „Catalog Symmetrica ediția 2023”.</t>
         </is>
@@ -820,6 +950,3879 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Categorie</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Produs</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>În catalog Symmetrica</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>În catalog Pavva</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>Cod Pavva</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Legendă culori</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Alegria Antica</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>PAV 04</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verde – Pe site</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Produsul e publicat pe site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Amplio Mix Color</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>PAV 09 / 228</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Albastru – Symmetrica</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Produsul apare în catalogul Symmetrica 2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Arco</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>PAV 321</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Mov – Pavva</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Produsul apare în lista de prețuri Pavva 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Arco Antica</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>PAV 321</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Roșu – LIPSEȘTE</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Produsul NU e pe site și trebuie încărcat (numele și statusul sunt roșii).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Cammino Mix Color</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>PAV 235</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Alb – „Nu”</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Produsul nu apare în sursa respectivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Immagia</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>PAV 94 / 95</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Kombi</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>PAV 311 / 310 / 331</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Cum citești un rând</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Plaza Antica</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>PAV 113</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>Exemplu 1</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Verde + albastru + mov = produsul e pe site și în ambele cataloage. Totul e în regulă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Amplio Granito</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>PAV 48</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Exemplu 2</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Roșu + albastru + mov = lipsește de pe site, dar e în ambele cataloage → de încărcat primul.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Arca Romana</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Exemplu 3</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Roșu + albastru (fără mov) = lipsește de pe site, e doar la Symmetrica → de confirmat dacă îl producem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Arca Romana Granito</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Exemplu 4</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Roșu + mov (fără albastru) = lipsește de pe site, e doar în lista Pavva → de încărcat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Arco Granito</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>PAV 321</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Bareto</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Cammino Granito</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>PAV 21</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Cammino Onda</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Enviro</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>PAV 316</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Innova Abrasio</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>PAV 804 / 805 / 806 / 807</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Innova Rocca</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>PAV 804 / 805 / 806 / 807</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Innova Travertino</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>PAV 804 / 805 / 806 / 807</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Kombi Design</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>PAV 359</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Kombi Versa</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>PAV 401</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Kombi Versa Antica</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>PAV 402</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Lastra Natura</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Linea Emotione Abrasio</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Linea Emotione Mix Color (Emotione)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>PAV 231</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Magna</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>PAV 234</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Maxia Mix Color</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Miro</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>PAV 230</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Nobile</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>PAV 236</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Quadra Granito</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>PAV 14</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Quadra Onda</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Retta Granito</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>PAV 15</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Retta Onda</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Premium</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Travia Mix Color</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Alegria</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>PAV 44 / 04 / 03</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Cammino</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>PAV 21 / 25</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Dublu „T”</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>PAV 02 / 01 / 26</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Kubik</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>PAV 12</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Mirage</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>PAV 23</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Quadra</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>PAV 14 / 88</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Retta</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>PAV 24 / 15 / 19 / 60</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Metria</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>PAV 332</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Practico</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Safirio</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>PAV 330</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Pavele Standard</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Sarmia</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Amplio</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>PAV 407 / 09 / 48</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Dala mare</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>PAV 51 / 52</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Eco Natura</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>PAV 72 / 22</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Tetra</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>PAV 110 / 227</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Dală direcțională T1</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>PAV 103</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Dală direcțională T2</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>PAV 104</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Amenajare Grădină</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Dală mare acoperire</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>PAV 51</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Amenajare Grădină</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Elemente placare Rock</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>PAV 99</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Amenajare Grădină</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Elemente placare Rock Antica</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>PAV 99</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Amenajare Grădină</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Kit pentru gradina Yucatan Antica</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>PAV 85 / 86 / 108 / 175 / 176</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Amenajare Grădină</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Kit pentru grădină Yucatan</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>PAV 85 / 86 / 108 / 175 / 176</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Amenajare Grădină</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Treaptă grădină</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>PAV 78 / 79</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Garduri</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Kit pentru garduri Gardeo</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>PAV 81 / 82 / 293 / 294</t>
+        </is>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Garduri</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Gard Ventus Line (element + capac)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>PAV 326 / 327</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mare PAVV 32</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>PAV 32</t>
+        </is>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mare PAVV 55</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>PAV 55</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mare PAVV 65</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>PAV 65</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mare PAVV 66</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>PAV 66</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mica PAVV 30</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>PAV 30</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mica PAVV 303</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>PAV 303</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mica PAVV 37</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>PAV 37</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mica PAVV 57</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>PAV 57</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mica PAVV 64</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>PAV 64</t>
+        </is>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mijlocie PAVV 31</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>PAV 31</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mijlocie PAVV 73</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>PAV 73</t>
+        </is>
+      </c>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Bordura mijlocie PAVV 92</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>PAV 92</t>
+        </is>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Bordura racord PAVV 36</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>PAV 36</t>
+        </is>
+      </c>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Bordură mare PAV 33</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>PAV 33</t>
+        </is>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Bordură mare curbă PAV 119</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>PAV 119</t>
+        </is>
+      </c>
+      <c r="H75" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Bordură mare PAV 118</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>PAV 118</t>
+        </is>
+      </c>
+      <c r="H76" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Bordură mijlocie PAV 403</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>PAV 403</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Bordură mijlocie PAV 404</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>PAV 404</t>
+        </is>
+      </c>
+      <c r="H78" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Bordură Practico (SYMM 91)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Borduri</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Bordură Rock (SYMM 116)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Capac rigolă</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>PAV 49 / 97 / 98</t>
+        </is>
+      </c>
+      <c r="H81" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă acostament</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>PAV 102</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă adâncă PAVV 147</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>PAV 147</t>
+        </is>
+      </c>
+      <c r="H83" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă cu fantă</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>PAV 295</t>
+        </is>
+      </c>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă mare și mică</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>PAV 39 / 35</t>
+        </is>
+      </c>
+      <c r="H85" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă pietonală</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>PAV 323</t>
+        </is>
+      </c>
+      <c r="H86" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă trapez</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PAV 115</t>
+        </is>
+      </c>
+      <c r="H87" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Rigolă șant tip ”L”</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>PAV 134</t>
+        </is>
+      </c>
+      <c r="H88" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Casiu</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>PAV 192</t>
+        </is>
+      </c>
+      <c r="H89" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Dale pereu</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>PAV 364 / 365 / 366</t>
+        </is>
+      </c>
+      <c r="H90" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>Dală acostament</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>PAV 304</t>
+        </is>
+      </c>
+      <c r="H91" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Rigolă adâncă PAV 320</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>PAV 320</t>
+        </is>
+      </c>
+      <c r="H92" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Rigole</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Rigolă șanț tip „U”</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>PAV 148</t>
+        </is>
+      </c>
+      <c r="H93" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Bolțari</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Bolțar fundație</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>PAV 123 / 124</t>
+        </is>
+      </c>
+      <c r="H94" s="16" t="inlineStr">
+        <is>
+          <t>Pe site</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Bolțari</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Bolțar zidărie</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>PAV 144 / 145</t>
+        </is>
+      </c>
+      <c r="H95" s="19" t="inlineStr">
+        <is>
+          <t>LIPSEȘTE de pe site</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H95"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -834,17 +4837,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Produs</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -1689,7 +5692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1711,42 +5714,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Gamă Symmetrica</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Produs Symmetrica</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Pagina catalog Symmetrica</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Pe site?</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Nume pe site</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>În catalog Pavva?</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Cod Pavva</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1758,43 +5761,43 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Linea Emotione Mix Color</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr"/>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr"/>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>Emotione – PAV 231</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
@@ -1806,39 +5809,39 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Linea Emotione Abrasio</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr"/>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr"/>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr"/>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr"/>
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
@@ -1850,2220 +5853,2220 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Magna</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr"/>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>PAV 234</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Kombi</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Kombi</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>PAV 311 / 310 / 331</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Bareto</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr"/>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Alegria Antica</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>Alegria Antica</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>PAV 04</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Plaza Antica</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>Plaza Antica</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>PAV 113</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Arco Antica</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>Arco Antica</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Arco</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Arco</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Arco Granito</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr"/>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Arca Romana</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr"/>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Arca Romana Granito</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Retta Granito</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>PAV 15</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Cammino Granito</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>PAV 21</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Quadra Granito</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>PAV 14</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Amplio Granito</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>PAV 48</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Retta Onda</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr"/>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Cammino Onda</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr"/>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Quadra Onda</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr"/>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr"/>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr"/>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr"/>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Travia Mix Color</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Cammino Mix Color</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>Cammino Mix Color</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>PAV 235</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Amplio Mix Color</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>Amplio Mix Color</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>PAV 09 / 228</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Maxia Mix Color</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr"/>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr"/>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Lastra Natura</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr"/>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr"/>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Symmetrica Select</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Immagia</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>Immagia</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>PAV 94 / 95</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>Kit pentru grădină Yucatan</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>Kit pentru grădină Yucatan</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>PAV 85 / 86 / 108 / 175 / 176</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>Kit pentru grădină Yucatan Antica</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>Kit pentru gradina Yucatan Antica</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>PAV 85 / 86 / 108 / 175 / 176</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>Dală mare acoperire</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>Dală mare acoperire</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>PAV 51</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>Kit pentru grădină Gardeo</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>Kit pentru garduri Gardeo</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>PAV 81 / 82 / 293 / 294</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>Element placare Rock</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>Elemente placare Rock</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>PAV 99</t>
         </is>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>Element placare Rock Antica</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>Elemente placare Rock Antica</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>PAV 99</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Grădină</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>Treaptă grădină</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>Treaptă grădină</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>PAV 78 / 79</t>
         </is>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Safirio</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr"/>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>PAV 330</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Sarmia</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr"/>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr"/>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Alegria</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>Alegria</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>PAV 44 / 04 / 03</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Practico</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Cammino</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>Cammino</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>PAV 21 / 25</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>Quadra</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>Quadra</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>PAV 14 / 88</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>Retta</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>Retta</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
         <is>
           <t>PAV 24 / 15 / 19 / 60</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr">
+      <c r="H40" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>Kubik</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
         <is>
           <t>Kubik</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>PAV 12</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H41" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>Dublu „T”</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
         <is>
           <t>Dublu „T”</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
         <is>
           <t>PAV 02 / 01 / 26</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
+      <c r="H42" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>Pavaj clasic</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>Mirage</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="21" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
         <is>
           <t>Mirage</t>
         </is>
       </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>PAV 23</t>
         </is>
       </c>
-      <c r="H43" s="13" t="inlineStr">
+      <c r="H43" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>Dale</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Amplio</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
         <is>
           <t>Amplio</t>
         </is>
       </c>
-      <c r="F44" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
         <is>
           <t>PAV 407 / 09 / 48</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H44" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Dale</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Tetra</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="21" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>Tetra</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
         <is>
           <t>PAV 110 / 227</t>
         </is>
       </c>
-      <c r="H45" s="13" t="inlineStr">
+      <c r="H45" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Dale</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>Eco Natura</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="21" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
         <is>
           <t>Eco Natura</t>
         </is>
       </c>
-      <c r="F46" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
         <is>
           <t>PAV 72 / 22</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H46" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>Bordură Rock (SYMM 116)</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>35, 53</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr"/>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr"/>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G47" s="20" t="inlineStr"/>
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 30</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="21" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 30</t>
         </is>
       </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
         <is>
           <t>PAV 30</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
+      <c r="H48" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 303</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 303</t>
         </is>
       </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>PAV 303</t>
         </is>
       </c>
-      <c r="H49" s="13" t="inlineStr">
+      <c r="H49" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>Bordură Practico (SYMM 91)</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Nu</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr"/>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr"/>
+      <c r="H50" s="20" t="inlineStr">
         <is>
           <t>Lipsește de pe site</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 37</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>52, 55</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 37</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>PAV 37</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="H51" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 64</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C52" s="21" t="inlineStr">
         <is>
           <t>52, 55</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 64</t>
         </is>
       </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
         <is>
           <t>PAV 64</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="H52" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>Bordură mică SYMM 57</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C53" s="21" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
         <is>
           <t>Bordura mica PAVV 57</t>
         </is>
       </c>
-      <c r="F53" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
         <is>
           <t>PAV 57</t>
         </is>
       </c>
-      <c r="H53" s="13" t="inlineStr">
+      <c r="H53" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>Bordură mijlocie SYMM 73</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C54" s="21" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
         <is>
           <t>Bordura mijlocie PAVV 73</t>
         </is>
       </c>
-      <c r="F54" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
         <is>
           <t>PAV 73</t>
         </is>
       </c>
-      <c r="H54" s="13" t="inlineStr">
+      <c r="H54" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>Bordură mijlocie SYMM 31</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="21" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>Bordura mijlocie PAVV 31</t>
         </is>
       </c>
-      <c r="F55" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
         <is>
           <t>PAV 31</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
+      <c r="H55" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>Bordură mijlocie SYMM 92</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" s="21" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="inlineStr">
         <is>
           <t>Bordura mijlocie PAVV 92</t>
         </is>
       </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="F56" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr">
         <is>
           <t>PAV 92</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr">
+      <c r="H56" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>Rigole</t>
         </is>
       </c>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>Rigolă mică (SYMM 39)</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" s="21" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="inlineStr">
         <is>
           <t>Rigolă mare și mică</t>
         </is>
       </c>
-      <c r="F57" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="F57" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="inlineStr">
         <is>
           <t>PAV 39</t>
         </is>
       </c>
-      <c r="H57" s="13" t="inlineStr">
+      <c r="H57" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>Rigole</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B58" s="21" t="inlineStr">
         <is>
           <t>Rigolă mare (SYMM 35)</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C58" s="21" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="inlineStr">
         <is>
           <t>Rigolă mare și mică</t>
         </is>
       </c>
-      <c r="F58" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G58" s="21" t="inlineStr">
         <is>
           <t>PAV 35</t>
         </is>
       </c>
-      <c r="H58" s="13" t="inlineStr">
+      <c r="H58" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>Rigole</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>Rigolă pietonală (SYMM 125)</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="21" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
         <is>
           <t>Rigolă pietonală</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
         <is>
           <t>PAV 323</t>
         </is>
       </c>
-      <c r="H59" s="13" t="inlineStr">
+      <c r="H59" s="21" t="inlineStr">
         <is>
           <t>Pe site</t>
         </is>
@@ -4075,7 +8078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4099,52 +8102,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Nr.</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Produs</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Categorie pe site (propusă)</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Sursă</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Cod Pavva</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Pag. catalog Pavva</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Pag. catalog Symmetrica</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Grosime</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Dimensiuni</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Culori</t>
         </is>
@@ -4156,55 +8159,55 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
+      <c r="A2" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Arco Granito</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>PAV 321</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>115×85, 115×73×102, 115×115 mm (3 forme)</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="20" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
@@ -4216,55 +8219,55 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Retta Granito</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>PAV 15</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>200×100 mm</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
@@ -4276,55 +8279,55 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Quadra Granito</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>PAV 14</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>200×200 mm</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="20" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>Doar Pavva</t>
         </is>
@@ -4336,838 +8339,838 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Cammino Granito</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>PAV 21</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>300×200 mm</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Amplio Granito</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>PAV 48</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>400×400 mm</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>portocaliu, antracit, crem, alb</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Magna</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>PAV 234</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>400×300 mm</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>crem-maro, alb-portocaliu-antracit, alb-travertin, alb-antracit</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Linea Emotione Mix Color (Emotione)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>PAV 231</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Pavva: 600×300 mm · Symmetrica: 20×30, 30×30, 30×40, 30×60, 20×40, 40×40, 40×60 cm</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>crem-maro, alb-portocaliu-antracit, alb-antracit, alb-travertin</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Safirio</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Pavele Standard</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Symmetrica + Pavva</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>PAV 330</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Pavva 6 cm · Symmetrica 4 cm</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>140×140 mm</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>alb, gri, antracit</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Linea Emotione Abrasio</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>20×30, 30×30, 30×40, 30×60, 20×40, 40×40, 40×60 cm</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>alb, gri, antracit, crem, maro</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Bareto</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>8 cm</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>30/40/50 × 12,5 și 30/40/50 × 16,5 cm (pachet)</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>alb, gri, antracit</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Arca Romana</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>12×16,5, 12×13, 12×10,5, 12×12, 12×18 cm (pachet 1 mp)</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>alb, gri, antracit, roșu, maro, portocaliu, crem</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Arca Romana Granito</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>12×16,5, 12×13, 12×10,5, 12×12, 12×18 cm (pachet 1 mp)</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>alb, gri, antracit, portocaliu, roșu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Retta Onda</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>20×10 cm</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Cammino Onda</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>20×30 cm</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Quadra Onda</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>20×20 cm</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Travia Mix Color</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>21×14, 14×14 cm (pachet 1,1 mp)</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Maxia Mix Color</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="14" t="inlineStr"/>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr"/>
+      <c r="F18" s="22" t="inlineStr"/>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>10 cm</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>80×62 cm</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>alb, gri, antracit, alb-antracit, alb-portocaliu, portocaliu-antracit</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>Lastra Natura</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Pavele Premium</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr"/>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr"/>
+      <c r="F19" s="22" t="inlineStr"/>
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>54×36, 36×36, 18×36 cm</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>portocaliu-antracit, gri-portocaliu-antracit, alb-antracit, alb-portocaliu</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>Sarmia</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Pavele Standard</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="14" t="inlineStr"/>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr"/>
+      <c r="F20" s="22" t="inlineStr"/>
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>6 cm</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>25×15 cm</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>alb, gri, antracit</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Practico</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Pavele Standard</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr"/>
-      <c r="F21" s="14" t="inlineStr"/>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr"/>
+      <c r="F21" s="22" t="inlineStr"/>
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>4 cm și 7 cm</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>15×10 cm</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>gri, antracit, roșu, maro, portocaliu</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Bordură Rock (SYMM 116)</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="14" t="inlineStr"/>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr"/>
+      <c r="F22" s="22" t="inlineStr"/>
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>35, 53</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>înălțime 12 cm</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>50×10 cm</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>gri, gri-portocaliu-antracit</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Bordură Practico (SYMM 91)</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>Borduri</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>Doar Symmetrica</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr"/>
-      <c r="F23" s="14" t="inlineStr"/>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr"/>
+      <c r="F23" s="22" t="inlineStr"/>
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>12 cm</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>24×6 cm</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>gri, roșu, portocaliu, maro, antracit</t>
         </is>
@@ -6145,7 +10148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6165,42 +10168,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Nr.</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Produs Symmetrica</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Categorie pe site (propusă)</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Pagina catalog Symmetrica</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Grosime</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Dimensiuni</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Culori</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Pe site?</t>
         </is>
